--- a/resources/Book1.xlsx
+++ b/resources/Book1.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpro/Documents/GitHub/meal-mentor/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06FE09B-A86A-B54C-BB46-D9C56D1420F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8F4720-2E73-074D-9838-A658246FB90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16420" xr2:uid="{F3634CFA-271D-AE48-B24E-08D60C2652A3}"/>
+    <workbookView xWindow="28800" yWindow="600" windowWidth="23600" windowHeight="14240" xr2:uid="{F3634CFA-271D-AE48-B24E-08D60C2652A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$4</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +38,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+  <si>
+    <t>vyalov_001</t>
+  </si>
   <si>
     <t>id</t>
   </si>
@@ -69,23 +76,79 @@
     <t>chapter</t>
   </si>
   <si>
-    <t>body_knowledge</t>
-  </si>
-  <si>
-    <t>body_organs</t>
-  </si>
-  <si>
-    <t>Желудочно-кишечный тракт представляет собой некую «трубу» или трубку. Эта труба имеет направление движения сверху вниз, так движется пища, только в одну сторону. При движении в обратную сторону начинаются проблемы. По мере продвижения по трубке происходят разные пищеварительные процессы. Делим эту трубу на разделы: пищевод, желудок, кишечник. Какие-то органы длиннее, а другие короче: желчный пузырь, поджелудочную железу, печень. Самое важное для работы пищеварения: места выделения ферментов, кислоты и желчи, и места переваривания и всасывания белков, жиров и углеводов.</t>
+    <t>body_structure</t>
+  </si>
+  <si>
+    <t>Желудочно-кишечный тракт представляет собой последовательную систему органов, через которые проходит пища: пищевод, желудок и кишечник. Пища продвигается по этой системе сверху вниз, и нормальное пищеварение предполагает движение в одном направлении.</t>
+  </si>
+  <si>
+    <t>По мере продвижения пищи по желудочно-кишечному тракту происходят разные процессы пищеварения. Важную роль играют места выделения ферментов, желудочной кислоты и желчи, которые участвуют в переваривании пищи.</t>
+  </si>
+  <si>
+    <t>digestive_process</t>
+  </si>
+  <si>
+    <t>vyalov_002</t>
+  </si>
+  <si>
+    <t>vyalov_003</t>
+  </si>
+  <si>
+    <t>nutrient_absorption</t>
+  </si>
+  <si>
+    <t>Разные отделы желудочно-кишечного тракта отвечают не только за переваривание пищи, но и за всасывание питательных веществ. В этих процессах участвуют ферменты, кислоты и желчь, обеспечивающие расщепление белков, жиров и углеводов.</t>
+  </si>
+  <si>
+    <t>["digestion","gastrointestinal","body_structure"]</t>
+  </si>
+  <si>
+    <t>["digestion","enzymes","bile"]</t>
+  </si>
+  <si>
+    <t>["digestion","absorption","macronutrients"]</t>
+  </si>
+  <si>
+    <t>1_digestion</t>
+  </si>
+  <si>
+    <t>recommendation</t>
+  </si>
+  <si>
+    <t>warning</t>
+  </si>
+  <si>
+    <t>deficiency_pattern</t>
+  </si>
+  <si>
+    <t>doctor_referral</t>
+  </si>
+  <si>
+    <t>symptom_relation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -111,10 +174,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,74 +511,176 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AC38FC-6192-DA4D-A0DA-1ECC1B1BA9D0}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="118.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="118.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86195BA0-4F0A-5F4C-95ED-D76F2BA1F7D3}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="85" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
